--- a/docs/ejemplos-importacion/cuotas.xlsx
+++ b/docs/ejemplos-importacion/cuotas.xlsx
@@ -1,41 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\Comisariato Web\sistema-comisariato-web\docs\ejemplos-importacion\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A0755E-9E3A-40FC-BB9D-0418B9A3BD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="cuotas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+  <si>
+    <t>creditoId</t>
+  </si>
+  <si>
+    <t>numeroCuota</t>
+  </si>
+  <si>
+    <t>monto</t>
+  </si>
+  <si>
+    <t>fechaPago</t>
+  </si>
+  <si>
+    <t>CRD-H01</t>
+  </si>
+  <si>
+    <t>10/06/2026</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>CRD-H02</t>
+  </si>
+  <si>
+    <t>CRD-H03</t>
+  </si>
+  <si>
+    <t>CRD-H05</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,7 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -73,6 +94,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,26 +426,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>creditoId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>numeroCuota</v>
-      </c>
-      <c r="C1" t="str">
-        <v>monto</v>
-      </c>
-      <c r="D1" t="str">
-        <v>fechaPago</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>CRD-H01</v>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -424,13 +454,13 @@
       <c r="C2">
         <v>817</v>
       </c>
-      <c r="D2" s="1" t="d">
-        <v>2026-04-10T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>CRD-H01</v>
+      <c r="D2" s="1">
+        <v>46122.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -438,13 +468,13 @@
       <c r="C3">
         <v>817</v>
       </c>
-      <c r="D3" s="1" t="d">
-        <v>2026-05-10T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>CRD-H01</v>
+      <c r="D3" s="1">
+        <v>46152.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -452,13 +482,13 @@
       <c r="C4">
         <v>817</v>
       </c>
-      <c r="D4" t="str">
-        <v>10/06/2026</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>CRD-H01</v>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -466,13 +496,13 @@
       <c r="C5">
         <v>817</v>
       </c>
-      <c r="D5" t="str">
-        <v>2026-07-10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>CRD-H02</v>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -480,13 +510,13 @@
       <c r="C6">
         <v>480</v>
       </c>
-      <c r="D6" s="1" t="d">
-        <v>2026-03-05T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>CRD-H02</v>
+      <c r="D6" s="1">
+        <v>46086.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -494,13 +524,13 @@
       <c r="C7">
         <v>480</v>
       </c>
-      <c r="D7" s="1" t="d">
-        <v>2026-04-05T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>CRD-H02</v>
+      <c r="D7" s="1">
+        <v>46117.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -508,13 +538,13 @@
       <c r="C8">
         <v>480</v>
       </c>
-      <c r="D8" s="1" t="d">
-        <v>2026-05-05T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CRD-H03</v>
+      <c r="D8" s="1">
+        <v>46147.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -522,13 +552,13 @@
       <c r="C9">
         <v>508</v>
       </c>
-      <c r="D9" s="1" t="d">
-        <v>2026-07-18T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>CRD-H03</v>
+      <c r="D9" s="1">
+        <v>46221.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -536,13 +566,13 @@
       <c r="C10">
         <v>508</v>
       </c>
-      <c r="D10" s="1" t="d">
-        <v>2026-08-18T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>CRD-H05</v>
+      <c r="D10" s="1">
+        <v>46252.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>9</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -550,55 +580,43 @@
       <c r="C11">
         <v>240</v>
       </c>
-      <c r="D11" s="1" t="d">
-        <v>2026-10-02T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>CRD-H04</v>
+      <c r="D11" s="1">
+        <v>46297.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
       </c>
       <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>817</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46244.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
         <v>1</v>
-      </c>
-      <c r="C12">
-        <v>520</v>
-      </c>
-      <c r="D12" s="1" t="d">
-        <v>2026-09-01T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>CRD-H01</v>
-      </c>
-      <c r="B13">
-        <v>13</v>
       </c>
       <c r="C13">
         <v>817</v>
       </c>
-      <c r="D13" s="1" t="d">
-        <v>2026-08-10T12:00:00.000Z</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>CRD-H01</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>817</v>
-      </c>
-      <c r="D14" s="1" t="d">
-        <v>2026-04-10T12:00:00.000Z</v>
-      </c>
-    </row>
+      <c r="D13" s="1">
+        <v>46122.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D14"/>
+    <ignoredError sqref="A1:D11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>